--- a/artfynd/A 35310-2024 artfynd.xlsx
+++ b/artfynd/A 35310-2024 artfynd.xlsx
@@ -2683,7 +2683,7 @@
         <v>101123229</v>
       </c>
       <c r="B19" t="n">
-        <v>5179</v>
+        <v>5182</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 35310-2024 artfynd.xlsx
+++ b/artfynd/A 35310-2024 artfynd.xlsx
@@ -2683,7 +2683,7 @@
         <v>101123229</v>
       </c>
       <c r="B19" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
